--- a/output/2026-10-01_20_Malesia_Kelantan_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-01_20_Malesia_Kelantan_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -484,10 +484,9 @@
           <t>010-9086367 / 09-748 3386</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato tramite directory locali (NewPages, Cybo), elenco dealer GL Bosun/DongCheng e sito ufficiale mbj.com.my</t>
+          <t>Verificato tramite directory locali (NewPages, Cybo), elenco dealer GL Bosun/DongCheng e sito ufficiale mbj.com.my [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -502,7 +501,6 @@
           <t>Syarikat Unicorn Engineering</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -518,7 +516,6 @@
           <t>012-3886748</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Verificato come dealer autorizzato DongCheng/GL Bosun, indirizzo confermato</t>
@@ -536,7 +533,6 @@
           <t>Chop Hup Seng</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -552,10 +548,9 @@
           <t>012-921 2226</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Verificato tramite elenco dealer DongCheng/GL Bosun e directory locali (Yelp, Lookp)</t>
+          <t>Verificato tramite elenco dealer DongCheng/GL Bosun e directory locali (Yelp, Lookp) [DUPLICATO — vedi anche: 2026-10-01_17_Malesia_Kelantan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -570,7 +565,6 @@
           <t>Alibaba Hardware</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Kuala Krai, Kelantan</t>
@@ -586,7 +580,6 @@
           <t>014-2922036</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificato: indirizzo e telefono corrispondenti su directory locali ed elenco dealer DongCheng</t>
@@ -604,7 +597,6 @@
           <t>Cheng Yeap (KB) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -620,7 +612,6 @@
           <t>019-710 0683</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verificato tramite elenco dealer DongCheng, pagina Facebook aziendale e report CTOS</t>
@@ -638,7 +629,6 @@
           <t>G.M. Maju Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Gua Musang, Kelantan</t>
@@ -654,10 +644,9 @@
           <t>012-9566330</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Verificato tramite pagina Facebook aziendale ed elenco dealer DongCheng/GL Bosun</t>
+          <t>Verificato tramite pagina Facebook aziendale ed elenco dealer DongCheng/GL Bosun [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -672,7 +661,6 @@
           <t>Jaya Tunas Trading</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Tanah Merah, Kelantan</t>
@@ -688,7 +676,6 @@
           <t>017-9831388 / 017-9541023</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Verificato tramite elenco dealer DongCheng/GL Bosun, Facebook e Waze</t>
@@ -726,10 +713,9 @@
           <t>019-5641010 / 012-7497898</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verificato tramite sito ufficiale timuransetia.com.my, elenco dealer DongCheng e profilo EMIS/D&amp;B</t>
+          <t>Verificato tramite sito ufficiale timuransetia.com.my, elenco dealer DongCheng e profilo EMIS/D&amp;B [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -744,7 +730,6 @@
           <t>Ipaint Steel Marketing Sdn Bhd</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Kota Bharu (Pauh, Panji), Kelantan</t>
@@ -760,7 +745,6 @@
           <t>+6013 752 7732 / 012-9857277</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verificato tramite pagina Facebook aziendale, elenco dealer DongCheng Kelantan e profilo EMIS</t>
@@ -778,7 +762,6 @@
           <t>Komtar Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -858,7 +841,6 @@
           <t>Golden Excel Hardware Trading</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pasir Mas, Kelantan</t>
@@ -874,10 +856,9 @@
           <t>+6014-606 4222</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Verificato tramite Facebook aziendale, Bizmalay e Mapcarta</t>
+          <t>Verificato tramite Facebook aziendale, Bizmalay e Mapcarta [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -892,7 +873,6 @@
           <t>Ong Seng Chip Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -908,7 +888,6 @@
           <t>012-9596855</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Verificato tramite elenco ufficiale dealer PUMA (pumacare.my)</t>
@@ -926,7 +905,6 @@
           <t>Cheng Kwee Seong Motors &amp; Trading</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -942,7 +920,6 @@
           <t>012-9858336</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Verificato tramite elenco ufficiale dealer PUMA (pumacare.my)</t>
@@ -960,7 +937,6 @@
           <t>Syarikat Chang Tradin</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Kota Bharu, Kelantan</t>
@@ -976,7 +952,6 @@
           <t>09-748 4237</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Verificato come centro assistenza autorizzato Bosch (bosch-pt.com.my)</t>
@@ -1014,10 +989,9 @@
           <t>+609-7125 555 / +609-7124 444</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Verificato come dealer ufficiale Makita (makita.my), sito aziendale e OpenCorporates</t>
+          <t>Verificato come dealer ufficiale Makita (makita.my), sito aziendale e OpenCorporates [DUPLICATO — vedi anche: 2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1064,7 +1038,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
